--- a/Manuscript/Manuscript v.2/Supplemental Files/Appendix SX. Cluster Names and Neuroanatomical Regions.xlsx
+++ b/Manuscript/Manuscript v.2/Supplemental Files/Appendix SX. Cluster Names and Neuroanatomical Regions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabe\Desktop\multiome_poa\Manuscript\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabe\Desktop\multiome_poa\Manuscript\Manuscript v.2\Supplemental Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F15DE72-A5BE-442B-88AD-67F9FFE81402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D9D366-2BE0-4A29-9983-0EBEB6AAB66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33525" yWindow="1575" windowWidth="15315" windowHeight="14160" xr2:uid="{C177D0C4-0B28-43EB-B299-93A92F59A1D8}"/>
+    <workbookView xWindow="31860" yWindow="1335" windowWidth="15315" windowHeight="14160" xr2:uid="{C177D0C4-0B28-43EB-B299-93A92F59A1D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -161,37 +161,37 @@
     <t>Region</t>
   </si>
   <si>
-    <t>Subpallium</t>
-  </si>
-  <si>
-    <t>Preoptic Area</t>
-  </si>
-  <si>
-    <t>Pallium</t>
-  </si>
-  <si>
-    <t>Ventral Optic Tract</t>
-  </si>
-  <si>
-    <t>Habenular Nuclei</t>
-  </si>
-  <si>
-    <t>Tertiary Gustatory Nucleus</t>
-  </si>
-  <si>
-    <t>Vsst</t>
-  </si>
-  <si>
-    <t>Vs-m</t>
-  </si>
-  <si>
-    <t>Diencephalon</t>
-  </si>
-  <si>
-    <t>Lateral Tuberal Nuclei</t>
-  </si>
-  <si>
     <t>7_Pall_Glut</t>
+  </si>
+  <si>
+    <t>ventral somatostatin nucleus</t>
+  </si>
+  <si>
+    <t>medial part of the supracommissural nucleus of the ventral telencephalon</t>
+  </si>
+  <si>
+    <t>lateral tuberal nuclei</t>
+  </si>
+  <si>
+    <t>diencephalon</t>
+  </si>
+  <si>
+    <t>subpallium</t>
+  </si>
+  <si>
+    <t>habenular huclei</t>
+  </si>
+  <si>
+    <t>ventral optic tract</t>
+  </si>
+  <si>
+    <t>pallium</t>
+  </si>
+  <si>
+    <t>preoptic area</t>
+  </si>
+  <si>
+    <t>yertiary gustatory nucleus</t>
   </si>
 </sst>
 </file>
@@ -596,7 +596,7 @@
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -632,7 +632,7 @@
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -646,7 +646,7 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -671,7 +671,7 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -679,13 +679,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -699,7 +699,7 @@
         <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -724,7 +724,7 @@
         <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -771,7 +771,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -829,7 +829,7 @@
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -854,7 +854,7 @@
         <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -868,7 +868,7 @@
         <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -882,7 +882,7 @@
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -896,7 +896,7 @@
         <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
